--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/08,09,26 Останкино Сыры/дв 08,09,26 лгрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/08,09,26 Останкино Сыры/дв 08,09,26 лгрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\08,09,26 Останкино Сыры\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C94247-9FB0-4530-B03B-280D291098CB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FFD8AB-F432-4D4A-8917-0E1FCB838C3C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -166,9 +166,6 @@
     <t>4421577 Спред растительно-сливочный "Сливочный вкус" 82,5% 180гр  Останкино</t>
   </si>
   <si>
-    <t>03,09,26 - нет на заводе / 27,08,26 - нет на заводе / 24,08,26 - нет на заводе / 30,07,26 - нет на заводе / 175шт в уценку (24,07,26)</t>
-  </si>
-  <si>
     <t>4421584 Спред растительно-сливочный "Сливочный вкус" 72,5% 180гр  Останкино</t>
   </si>
   <si>
@@ -300,6 +297,9 @@
   <si>
     <t>14,09,</t>
   </si>
+  <si>
+    <t>10,09,26 - нет на заводе / 03,09,26 - нет на заводе / 27,08,26 - нет на заводе / 24,08,26 - нет на заводе / 30,07,26 - нет на заводе / 175шт в уценку (24,07,26)</t>
+  </si>
 </sst>
 </file>
 
@@ -346,7 +346,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -366,6 +366,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,7 +411,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -419,6 +425,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -901,10 +908,10 @@
         <v>15</v>
       </c>
       <c r="S3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>16</v>
@@ -993,7 +1000,7 @@
       </c>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1100,7 +1107,7 @@
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>1666</v>
+        <v>1642</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1247,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="AG6" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH6" s="1">
         <f t="shared" ref="AH6:AH42" si="3">G6*S6</f>
@@ -1629,9 +1636,8 @@
       <c r="S10" s="5">
         <v>12</v>
       </c>
-      <c r="T10" s="5">
-        <f>VLOOKUP(A10,заказ!A:B,2,0)</f>
-        <v>12</v>
+      <c r="T10" s="13">
+        <v>0</v>
       </c>
       <c r="U10" s="1" t="e">
         <f t="shared" si="5"/>
@@ -1672,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="AH10" s="1">
         <f t="shared" si="3"/>
@@ -1696,7 +1702,7 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>36</v>
@@ -1732,9 +1738,8 @@
       <c r="S11" s="5">
         <v>12</v>
       </c>
-      <c r="T11" s="5">
-        <f>VLOOKUP(A11,заказ!A:B,2,0)</f>
-        <v>12</v>
+      <c r="T11" s="13">
+        <v>0</v>
       </c>
       <c r="U11" s="1" t="e">
         <f t="shared" si="5"/>
@@ -1775,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="AH11" s="1">
         <f t="shared" si="3"/>
@@ -1799,7 +1804,7 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>41</v>
@@ -1901,7 +1906,7 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>36</v>
@@ -1981,7 +1986,7 @@
         <v>1</v>
       </c>
       <c r="AG13" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AH13" s="1">
         <f t="shared" si="3"/>
@@ -2005,7 +2010,7 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>36</v>
@@ -2115,7 +2120,7 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>36</v>
@@ -2195,7 +2200,7 @@
         <v>10.8</v>
       </c>
       <c r="AG15" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" si="3"/>
@@ -2219,7 +2224,7 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>36</v>
@@ -2329,7 +2334,7 @@
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>36</v>
@@ -2413,7 +2418,7 @@
         <v>46.2</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AH17" s="1">
         <f t="shared" si="3"/>
@@ -2437,7 +2442,7 @@
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>36</v>
@@ -2547,7 +2552,7 @@
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>36</v>
@@ -2651,7 +2656,7 @@
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>36</v>
@@ -2733,7 +2738,7 @@
         <v>22.8</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AH20" s="1">
         <f t="shared" si="3"/>
@@ -2757,7 +2762,7 @@
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>36</v>
@@ -2833,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="AG21" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AH21" s="1">
         <f t="shared" si="3"/>
@@ -2857,7 +2862,7 @@
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>36</v>
@@ -2937,7 +2942,7 @@
         <v>1.2</v>
       </c>
       <c r="AG22" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AH22" s="1">
         <f t="shared" si="3"/>
@@ -2961,7 +2966,7 @@
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>36</v>
@@ -3063,7 +3068,7 @@
     </row>
     <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>36</v>
@@ -3175,7 +3180,7 @@
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>36</v>
@@ -3199,7 +3204,7 @@
         <v>150</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1">
@@ -3261,7 +3266,7 @@
         <v>18.2</v>
       </c>
       <c r="AG25" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AH25" s="1">
         <f t="shared" si="3"/>
@@ -3285,7 +3290,7 @@
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>36</v>
@@ -3397,7 +3402,7 @@
     </row>
     <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>36</v>
@@ -3507,7 +3512,7 @@
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>36</v>
@@ -3613,7 +3618,7 @@
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>36</v>
@@ -3725,7 +3730,7 @@
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>36</v>
@@ -3833,7 +3838,7 @@
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>41</v>
@@ -3907,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="AG31" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AH31" s="1">
         <f t="shared" si="3"/>
@@ -3931,7 +3936,7 @@
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>36</v>
@@ -4037,7 +4042,7 @@
     </row>
     <row r="33" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>36</v>
@@ -4147,7 +4152,7 @@
     </row>
     <row r="34" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>41</v>
@@ -4227,7 +4232,7 @@
         <v>0.68840000000000001</v>
       </c>
       <c r="AG34" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH34" s="1">
         <f t="shared" si="3"/>
@@ -4251,7 +4256,7 @@
     </row>
     <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>41</v>
@@ -4359,7 +4364,7 @@
     </row>
     <row r="36" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>36</v>
@@ -4465,7 +4470,7 @@
     </row>
     <row r="37" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>36</v>
@@ -4569,7 +4574,7 @@
     </row>
     <row r="38" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>36</v>
@@ -4679,7 +4684,7 @@
     </row>
     <row r="39" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>36</v>
@@ -4791,7 +4796,7 @@
     </row>
     <row r="40" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>41</v>
@@ -4869,7 +4874,7 @@
         <v>3.7711999999999999</v>
       </c>
       <c r="AG40" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AH40" s="1">
         <f t="shared" si="3"/>
@@ -4893,7 +4898,7 @@
     </row>
     <row r="41" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>36</v>
@@ -5003,7 +5008,7 @@
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>41</v>
@@ -5088,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="AG42" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH42" s="1">
         <f t="shared" si="3"/>
@@ -28438,7 +28443,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -28446,7 +28451,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3">
         <v>312</v>
@@ -28454,7 +28459,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4">
         <v>528</v>
@@ -28462,7 +28467,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5">
         <v>128</v>
@@ -28470,7 +28475,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>32</v>
@@ -28478,7 +28483,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B7">
         <v>180</v>
@@ -28486,7 +28491,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B8">
         <v>170</v>
@@ -28494,7 +28499,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B9">
         <v>20</v>
@@ -28502,7 +28507,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -28510,7 +28515,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B11">
         <v>48</v>
@@ -28518,7 +28523,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12">
         <v>33</v>
@@ -28526,7 +28531,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13">
         <v>16</v>
@@ -28534,7 +28539,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14">
         <v>140</v>
@@ -28542,7 +28547,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15">
         <v>10</v>
@@ -28550,7 +28555,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B16">
         <v>15</v>
